--- a/tools/excel/3xlsx/map.xlsx
+++ b/tools/excel/3xlsx/map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>排序权重</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>动物池</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>场景预制体</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +479,16 @@
           <t>sortPriority</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>animals</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>scenePath</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +516,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>array.uint</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -521,6 +551,16 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>all</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>client</t>
         </is>
       </c>
     </row>
@@ -530,7 +570,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>路边咖啡</t>
+          <t>沙漠</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -538,6 +578,16 @@
       </c>
       <c r="E7" t="n">
         <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6|2|12|21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Map/Chapter1_Desert</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -546,7 +596,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>十字路口</t>
+          <t>沼泽</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -554,6 +604,11 @@
       </c>
       <c r="E8" t="n">
         <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8|14|1|3</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -562,14 +617,82 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群山村落</t>
+          <t>草原</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5|7|15|19|9|2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>热带草原</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16|11|22|10|18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>竹林</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4|20|9|17|13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>戈壁</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6|21|12|15|5</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/map.xlsx
+++ b/tools/excel/3xlsx/map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>场景预制体</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>解锁分数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>scenePath</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>unlockScore</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,6 +576,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>client</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -589,6 +609,9 @@
           <t>Map/Chapter1_Desert</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -600,7 +623,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -609,6 +632,9 @@
         <is>
           <t>8|14|1|3</t>
         </is>
+      </c>
+      <c r="H8" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +647,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -630,6 +656,9 @@
         <is>
           <t>5|7|15|19|9|2</t>
         </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
@@ -642,7 +671,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -651,6 +680,9 @@
         <is>
           <t>16|11|22|10|18</t>
         </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2500</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +695,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
@@ -672,6 +704,9 @@
         <is>
           <t>4|20|9|17|13</t>
         </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +719,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -693,6 +728,9 @@
         <is>
           <t>6|21|12|15|5</t>
         </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
